--- a/Project REBOUND Exit Survey_Jayden.xlsx
+++ b/Project REBOUND Exit Survey_Jayden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB9CD22-912C-41A8-A069-A7855FA23370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFA0D16-2D82-4592-AEF4-69E767FC9BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,7 +671,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -759,7 +758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45792.852905092594</v>
       </c>
@@ -839,7 +838,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45792.853796296295</v>
       </c>
@@ -999,7 +998,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45792.826458333337</v>
       </c>
@@ -1159,7 +1158,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="130.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45867.126331018517</v>
       </c>
@@ -1319,7 +1318,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45881.251562500001</v>
       </c>
@@ -1399,7 +1398,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45890.860555555555</v>
       </c>
@@ -1479,7 +1478,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45952.100810185184</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="116" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45959.118900462963</v>
       </c>
@@ -1720,18 +1719,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z13" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="True"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="15">
-      <filters>
-        <filter val="COMP1350 - Introduction to Database Design and Management"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C1 D1 G1 I1 L1 M1 N1 O1 P1 Q1 R1 S1 T1 U1 V1 W1 X1 Y1 Z1 C2:C13 D2:D13 G2:G13 I2:I13 L2:L13 M2:M13 N2:N13 O2:O13 P2:P13 Q2:Q13 R2:R13 S2:S13 T2:T13 U2:U13 V2:V13 W2:W13 X2:X13 Y2:Y13 Z2:Z13" numberStoredAsText="1"/>
